--- a/Gráficos Abs G8.xlsx
+++ b/Gráficos Abs G8.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\david\OneDrive\Documentos\EAFIT\Tesis de grado\AQUAFUNGI G8\Datos y scripts de gráficos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FAAEABBD-7CDF-4DF7-8BDF-00D8C4A66423}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC281299-6633-400D-A62A-1BA4302125A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" firstSheet="4" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" firstSheet="5" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PLDJ 2025" sheetId="2" r:id="rId1"/>
@@ -24,6 +24,7 @@
     <sheet name="PLER 2026-2 LMM" sheetId="9" r:id="rId9"/>
     <sheet name="PYSA" sheetId="10" r:id="rId10"/>
     <sheet name="PYSA LMM" sheetId="11" r:id="rId11"/>
+    <sheet name="UNIFICADOS" sheetId="12" r:id="rId12"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -35,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2021" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2320" uniqueCount="20">
   <si>
     <t>Species</t>
   </si>
@@ -86,6 +87,15 @@
   </si>
   <si>
     <t>Pholiota adiposa</t>
+  </si>
+  <si>
+    <t>Pleurotus djamor</t>
+  </si>
+  <si>
+    <t>Pleurotus eryngii</t>
+  </si>
+  <si>
+    <t>Pycnoporus sanguineus</t>
   </si>
 </sst>
 </file>
@@ -4098,18 +4108,1708 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6D9A9276-9712-4B98-A3BA-1E0B9C50C9A0}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:E23"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A2" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B2">
+        <v>3</v>
+      </c>
+      <c r="C2">
+        <v>0</v>
+      </c>
+      <c r="D2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2">
+        <v>2.0409999999999999</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A3" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B3">
+        <v>3</v>
+      </c>
+      <c r="C3">
+        <v>0</v>
+      </c>
+      <c r="D3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E3">
+        <v>1.966</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A4" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B4">
+        <v>3</v>
+      </c>
+      <c r="C4">
+        <v>0</v>
+      </c>
+      <c r="D4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E4">
+        <v>1.823</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A5" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5">
+        <v>3</v>
+      </c>
+      <c r="C5">
+        <v>16</v>
+      </c>
+      <c r="D5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E5">
+        <v>0.26400000000000001</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A6" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B6">
+        <v>3</v>
+      </c>
+      <c r="C6">
+        <v>16</v>
+      </c>
+      <c r="D6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E6">
+        <v>0.19900000000000001</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A7" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B7">
+        <v>3</v>
+      </c>
+      <c r="C7">
+        <v>16</v>
+      </c>
+      <c r="D7" t="s">
+        <v>10</v>
+      </c>
+      <c r="E7">
+        <v>0.20599999999999999</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A8" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B8">
+        <v>6</v>
+      </c>
+      <c r="C8">
+        <v>0</v>
+      </c>
+      <c r="D8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E8">
+        <v>1.097</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A9" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B9">
+        <v>6</v>
+      </c>
+      <c r="C9">
+        <v>0</v>
+      </c>
+      <c r="D9" t="s">
+        <v>9</v>
+      </c>
+      <c r="E9">
+        <v>1.9430000000000001</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A10" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B10">
+        <v>6</v>
+      </c>
+      <c r="C10">
+        <v>0</v>
+      </c>
+      <c r="D10" t="s">
+        <v>10</v>
+      </c>
+      <c r="E10">
+        <v>2.3130000000000002</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A11" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B11">
+        <v>6</v>
+      </c>
+      <c r="C11">
+        <v>16</v>
+      </c>
+      <c r="D11" t="s">
+        <v>8</v>
+      </c>
+      <c r="E11">
+        <v>0.224</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A12" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B12">
+        <v>6</v>
+      </c>
+      <c r="C12">
+        <v>16</v>
+      </c>
+      <c r="D12" t="s">
+        <v>9</v>
+      </c>
+      <c r="E12">
+        <v>0.14899999999999999</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A13" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B13">
+        <v>6</v>
+      </c>
+      <c r="C13">
+        <v>16</v>
+      </c>
+      <c r="D13" t="s">
+        <v>10</v>
+      </c>
+      <c r="E13">
+        <v>0.23400000000000001</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A14" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B14">
+        <v>9</v>
+      </c>
+      <c r="C14">
+        <v>0</v>
+      </c>
+      <c r="D14" t="s">
+        <v>8</v>
+      </c>
+      <c r="E14">
+        <v>2.0259999999999998</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A15" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B15">
+        <v>9</v>
+      </c>
+      <c r="C15">
+        <v>0</v>
+      </c>
+      <c r="D15" t="s">
+        <v>9</v>
+      </c>
+      <c r="E15">
+        <v>2.056</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A16" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B16">
+        <v>9</v>
+      </c>
+      <c r="C16">
+        <v>0</v>
+      </c>
+      <c r="D16" t="s">
+        <v>10</v>
+      </c>
+      <c r="E16">
+        <v>2.081</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A17" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B17">
+        <v>9</v>
+      </c>
+      <c r="C17">
+        <v>16</v>
+      </c>
+      <c r="D17" t="s">
+        <v>8</v>
+      </c>
+      <c r="E17">
+        <v>0.104</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A18" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B18">
+        <v>9</v>
+      </c>
+      <c r="C18">
+        <v>16</v>
+      </c>
+      <c r="D18" t="s">
+        <v>9</v>
+      </c>
+      <c r="E18">
+        <v>0.17799999999999999</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A19" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B19">
+        <v>9</v>
+      </c>
+      <c r="C19">
+        <v>16</v>
+      </c>
+      <c r="D19" t="s">
+        <v>10</v>
+      </c>
+      <c r="E19">
+        <v>0.17299999999999999</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A20" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B20" t="s">
+        <v>13</v>
+      </c>
+      <c r="C20">
+        <v>0</v>
+      </c>
+      <c r="D20" t="s">
+        <v>11</v>
+      </c>
+      <c r="E20">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A21" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B21" t="s">
+        <v>13</v>
+      </c>
+      <c r="C21">
+        <v>16</v>
+      </c>
+      <c r="D21" t="s">
+        <v>11</v>
+      </c>
+      <c r="E21">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A22" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B22" t="s">
+        <v>12</v>
+      </c>
+      <c r="C22">
+        <v>0</v>
+      </c>
+      <c r="D22" t="s">
+        <v>11</v>
+      </c>
+      <c r="E22">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A23" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B23" t="s">
+        <v>12</v>
+      </c>
+      <c r="C23">
+        <v>16</v>
+      </c>
+      <c r="D23" t="s">
+        <v>11</v>
+      </c>
+      <c r="E23">
+        <v>0.05</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{90137427-1E0F-4D84-AA08-2398EA51A033}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:G19"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A2" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B2">
+        <v>0</v>
+      </c>
+      <c r="C2">
+        <v>3</v>
+      </c>
+      <c r="D2">
+        <v>6</v>
+      </c>
+      <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G2">
+        <v>2.0409999999999999</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A3" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B3">
+        <v>0</v>
+      </c>
+      <c r="C3">
+        <v>3</v>
+      </c>
+      <c r="D3">
+        <v>6</v>
+      </c>
+      <c r="E3">
+        <v>0</v>
+      </c>
+      <c r="F3" t="s">
+        <v>9</v>
+      </c>
+      <c r="G3">
+        <v>1.966</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A4" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B4">
+        <v>0</v>
+      </c>
+      <c r="C4">
+        <v>3</v>
+      </c>
+      <c r="D4">
+        <v>6</v>
+      </c>
+      <c r="E4">
+        <v>0</v>
+      </c>
+      <c r="F4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G4">
+        <v>1.823</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A5" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5">
+        <v>0</v>
+      </c>
+      <c r="C5">
+        <v>3</v>
+      </c>
+      <c r="D5">
+        <v>6</v>
+      </c>
+      <c r="E5">
+        <v>16</v>
+      </c>
+      <c r="F5" t="s">
+        <v>8</v>
+      </c>
+      <c r="G5">
+        <v>0.26400000000000001</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A6" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B6">
+        <v>0</v>
+      </c>
+      <c r="C6">
+        <v>3</v>
+      </c>
+      <c r="D6">
+        <v>6</v>
+      </c>
+      <c r="E6">
+        <v>16</v>
+      </c>
+      <c r="F6" t="s">
+        <v>9</v>
+      </c>
+      <c r="G6">
+        <v>0.19900000000000001</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A7" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B7">
+        <v>0</v>
+      </c>
+      <c r="C7">
+        <v>3</v>
+      </c>
+      <c r="D7">
+        <v>6</v>
+      </c>
+      <c r="E7">
+        <v>16</v>
+      </c>
+      <c r="F7" t="s">
+        <v>10</v>
+      </c>
+      <c r="G7">
+        <v>0.20599999999999999</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A8" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B8">
+        <v>0.5</v>
+      </c>
+      <c r="C8">
+        <v>6</v>
+      </c>
+      <c r="D8">
+        <v>6</v>
+      </c>
+      <c r="E8">
+        <v>0</v>
+      </c>
+      <c r="F8" t="s">
+        <v>8</v>
+      </c>
+      <c r="G8">
+        <v>1.097</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A9" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B9">
+        <v>0.5</v>
+      </c>
+      <c r="C9">
+        <v>6</v>
+      </c>
+      <c r="D9">
+        <v>6</v>
+      </c>
+      <c r="E9">
+        <v>0</v>
+      </c>
+      <c r="F9" t="s">
+        <v>9</v>
+      </c>
+      <c r="G9">
+        <v>1.9430000000000001</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A10" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B10">
+        <v>0.5</v>
+      </c>
+      <c r="C10">
+        <v>6</v>
+      </c>
+      <c r="D10">
+        <v>6</v>
+      </c>
+      <c r="E10">
+        <v>0</v>
+      </c>
+      <c r="F10" t="s">
+        <v>10</v>
+      </c>
+      <c r="G10">
+        <v>2.3130000000000002</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A11" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B11">
+        <v>0.5</v>
+      </c>
+      <c r="C11">
+        <v>6</v>
+      </c>
+      <c r="D11">
+        <v>6</v>
+      </c>
+      <c r="E11">
+        <v>16</v>
+      </c>
+      <c r="F11" t="s">
+        <v>8</v>
+      </c>
+      <c r="G11">
+        <v>0.224</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A12" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B12">
+        <v>0.5</v>
+      </c>
+      <c r="C12">
+        <v>6</v>
+      </c>
+      <c r="D12">
+        <v>6</v>
+      </c>
+      <c r="E12">
+        <v>16</v>
+      </c>
+      <c r="F12" t="s">
+        <v>9</v>
+      </c>
+      <c r="G12">
+        <v>0.14899999999999999</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A13" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B13">
+        <v>0.5</v>
+      </c>
+      <c r="C13">
+        <v>6</v>
+      </c>
+      <c r="D13">
+        <v>6</v>
+      </c>
+      <c r="E13">
+        <v>16</v>
+      </c>
+      <c r="F13" t="s">
+        <v>10</v>
+      </c>
+      <c r="G13">
+        <v>0.23400000000000001</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A14" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B14">
+        <v>1</v>
+      </c>
+      <c r="C14">
+        <v>9</v>
+      </c>
+      <c r="D14">
+        <v>6</v>
+      </c>
+      <c r="E14">
+        <v>0</v>
+      </c>
+      <c r="F14" t="s">
+        <v>8</v>
+      </c>
+      <c r="G14">
+        <v>2.0259999999999998</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A15" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B15">
+        <v>1</v>
+      </c>
+      <c r="C15">
+        <v>9</v>
+      </c>
+      <c r="D15">
+        <v>6</v>
+      </c>
+      <c r="E15">
+        <v>0</v>
+      </c>
+      <c r="F15" t="s">
+        <v>9</v>
+      </c>
+      <c r="G15">
+        <v>2.056</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A16" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B16">
+        <v>1</v>
+      </c>
+      <c r="C16">
+        <v>9</v>
+      </c>
+      <c r="D16">
+        <v>6</v>
+      </c>
+      <c r="E16">
+        <v>0</v>
+      </c>
+      <c r="F16" t="s">
+        <v>10</v>
+      </c>
+      <c r="G16">
+        <v>2.081</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A17" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B17">
+        <v>1</v>
+      </c>
+      <c r="C17">
+        <v>9</v>
+      </c>
+      <c r="D17">
+        <v>6</v>
+      </c>
+      <c r="E17">
+        <v>16</v>
+      </c>
+      <c r="F17" t="s">
+        <v>8</v>
+      </c>
+      <c r="G17">
+        <v>0.104</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A18" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B18">
+        <v>1</v>
+      </c>
+      <c r="C18">
+        <v>9</v>
+      </c>
+      <c r="D18">
+        <v>6</v>
+      </c>
+      <c r="E18">
+        <v>16</v>
+      </c>
+      <c r="F18" t="s">
+        <v>9</v>
+      </c>
+      <c r="G18">
+        <v>0.17799999999999999</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A19" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B19">
+        <v>1</v>
+      </c>
+      <c r="C19">
+        <v>9</v>
+      </c>
+      <c r="D19">
+        <v>6</v>
+      </c>
+      <c r="E19">
+        <v>16</v>
+      </c>
+      <c r="F19" t="s">
+        <v>10</v>
+      </c>
+      <c r="G19">
+        <v>0.17299999999999999</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FCE7F3DC-73E1-43EF-B2BE-E206041AC004}">
+  <dimension ref="A1:E50"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A2" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B2" s="15">
+        <v>9</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" s="16">
+        <v>1.5669999999999999</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A3" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3">
+        <v>9</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="D3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E3" s="3">
+        <v>1.4359999999999999</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A4" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B4">
+        <v>9</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+      <c r="D4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E4" s="3">
+        <v>1.417</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A5" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5">
+        <v>9</v>
+      </c>
+      <c r="C5">
+        <v>3</v>
+      </c>
+      <c r="D5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E5" s="13">
+        <v>1.3540000000000001</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A6" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B6">
+        <v>9</v>
+      </c>
+      <c r="C6">
+        <v>3</v>
+      </c>
+      <c r="D6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E6" s="13">
+        <v>1.381</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A7" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B7">
+        <v>9</v>
+      </c>
+      <c r="C7">
+        <v>3</v>
+      </c>
+      <c r="D7" t="s">
+        <v>10</v>
+      </c>
+      <c r="E7" s="13">
+        <v>1.3919999999999999</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A8" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B8">
+        <v>9</v>
+      </c>
+      <c r="C8">
+        <v>6</v>
+      </c>
+      <c r="D8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E8" s="7">
+        <v>0.156</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A9" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B9">
+        <v>9</v>
+      </c>
+      <c r="C9">
+        <v>6</v>
+      </c>
+      <c r="D9" t="s">
+        <v>9</v>
+      </c>
+      <c r="E9" s="8">
+        <v>0.20100000000000001</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A10" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B10">
+        <v>9</v>
+      </c>
+      <c r="C10">
+        <v>6</v>
+      </c>
+      <c r="D10" t="s">
+        <v>10</v>
+      </c>
+      <c r="E10" s="7">
+        <v>0.183</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A11" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B11">
+        <v>9</v>
+      </c>
+      <c r="C11">
+        <v>9</v>
+      </c>
+      <c r="D11" t="s">
+        <v>8</v>
+      </c>
+      <c r="E11" s="13">
+        <v>1.2909999999999999</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A12" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B12">
+        <v>9</v>
+      </c>
+      <c r="C12">
+        <v>9</v>
+      </c>
+      <c r="D12" t="s">
+        <v>9</v>
+      </c>
+      <c r="E12" s="13">
+        <v>1.3120000000000001</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A13" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B13">
+        <v>9</v>
+      </c>
+      <c r="C13">
+        <v>9</v>
+      </c>
+      <c r="D13" t="s">
+        <v>10</v>
+      </c>
+      <c r="E13" s="13">
+        <v>1.335</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A14" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B14">
+        <v>9</v>
+      </c>
+      <c r="C14">
+        <v>13</v>
+      </c>
+      <c r="D14" t="s">
+        <v>8</v>
+      </c>
+      <c r="E14" s="7">
+        <v>6.9000000000000006E-2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A15" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B15">
+        <v>9</v>
+      </c>
+      <c r="C15">
+        <v>13</v>
+      </c>
+      <c r="D15" t="s">
+        <v>9</v>
+      </c>
+      <c r="E15" s="7">
+        <v>5.3999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A16" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B16">
+        <v>9</v>
+      </c>
+      <c r="C16">
+        <v>13</v>
+      </c>
+      <c r="D16" t="s">
+        <v>10</v>
+      </c>
+      <c r="E16" s="7">
+        <v>5.6000000000000001E-2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A17" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B17">
+        <v>9</v>
+      </c>
+      <c r="C17">
+        <v>16</v>
+      </c>
+      <c r="D17" t="s">
+        <v>8</v>
+      </c>
+      <c r="E17" s="11">
+        <v>0.46800000000000003</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A18" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B18">
+        <v>9</v>
+      </c>
+      <c r="C18">
+        <v>16</v>
+      </c>
+      <c r="D18" t="s">
+        <v>9</v>
+      </c>
+      <c r="E18" s="6">
+        <v>0.439</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A19" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B19">
+        <v>9</v>
+      </c>
+      <c r="C19">
+        <v>16</v>
+      </c>
+      <c r="D19" t="s">
+        <v>10</v>
+      </c>
+      <c r="E19" s="11">
+        <v>0.45600000000000002</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A20" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B20">
+        <v>9</v>
+      </c>
+      <c r="C20">
+        <v>1</v>
+      </c>
+      <c r="D20" t="s">
+        <v>8</v>
+      </c>
+      <c r="E20" s="12">
+        <v>2.044</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A21" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B21">
+        <v>9</v>
+      </c>
+      <c r="C21">
+        <v>1</v>
+      </c>
+      <c r="D21" t="s">
+        <v>9</v>
+      </c>
+      <c r="E21" s="12">
+        <v>2.0459999999999998</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A22" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B22">
+        <v>9</v>
+      </c>
+      <c r="C22">
+        <v>1</v>
+      </c>
+      <c r="D22" t="s">
+        <v>10</v>
+      </c>
+      <c r="E22" s="12">
+        <v>2.048</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A23" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B23">
+        <v>9</v>
+      </c>
+      <c r="C23">
+        <v>4</v>
+      </c>
+      <c r="D23" t="s">
+        <v>8</v>
+      </c>
+      <c r="E23" s="16">
+        <v>1.633</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A24" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B24">
+        <v>9</v>
+      </c>
+      <c r="C24">
+        <v>4</v>
+      </c>
+      <c r="D24" t="s">
+        <v>9</v>
+      </c>
+      <c r="E24" s="16">
+        <v>1.653</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A25" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B25">
+        <v>9</v>
+      </c>
+      <c r="C25">
+        <v>4</v>
+      </c>
+      <c r="D25" t="s">
+        <v>10</v>
+      </c>
+      <c r="E25" s="16">
+        <v>1.64</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A26" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B26">
+        <v>9</v>
+      </c>
+      <c r="C26">
+        <v>8</v>
+      </c>
+      <c r="D26" t="s">
+        <v>8</v>
+      </c>
+      <c r="E26" s="9">
+        <v>1.0660000000000001</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A27" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B27">
+        <v>9</v>
+      </c>
+      <c r="C27">
+        <v>8</v>
+      </c>
+      <c r="D27" t="s">
+        <v>9</v>
+      </c>
+      <c r="E27" s="9">
+        <v>1.0509999999999999</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A28" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B28">
+        <v>9</v>
+      </c>
+      <c r="C28">
+        <v>8</v>
+      </c>
+      <c r="D28" t="s">
+        <v>10</v>
+      </c>
+      <c r="E28" s="9">
+        <v>1.109</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A29" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B29">
+        <v>9</v>
+      </c>
+      <c r="C29">
+        <v>11</v>
+      </c>
+      <c r="D29" t="s">
+        <v>8</v>
+      </c>
+      <c r="E29" s="7">
+        <v>0.123</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A30" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B30">
+        <v>9</v>
+      </c>
+      <c r="C30">
+        <v>11</v>
+      </c>
+      <c r="D30" t="s">
+        <v>9</v>
+      </c>
+      <c r="E30" s="7">
+        <v>0.109</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A31" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B31">
+        <v>9</v>
+      </c>
+      <c r="C31">
+        <v>11</v>
+      </c>
+      <c r="D31" t="s">
+        <v>10</v>
+      </c>
+      <c r="E31" s="7">
+        <v>0.108</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A32" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B32">
+        <v>9</v>
+      </c>
+      <c r="C32">
+        <v>14</v>
+      </c>
+      <c r="D32" t="s">
+        <v>8</v>
+      </c>
+      <c r="E32" s="7">
+        <v>9.7000000000000003E-2</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A33" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B33">
+        <v>9</v>
+      </c>
+      <c r="C33">
+        <v>14</v>
+      </c>
+      <c r="D33" t="s">
+        <v>9</v>
+      </c>
+      <c r="E33" s="7">
+        <v>9.6000000000000002E-2</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A34" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B34">
+        <v>9</v>
+      </c>
+      <c r="C34">
+        <v>14</v>
+      </c>
+      <c r="D34" t="s">
+        <v>10</v>
+      </c>
+      <c r="E34" s="7">
+        <v>9.7000000000000003E-2</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A35" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B35">
+        <v>9</v>
+      </c>
+      <c r="C35">
+        <v>0</v>
+      </c>
+      <c r="D35" t="s">
+        <v>8</v>
+      </c>
+      <c r="E35">
+        <v>2.056</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A36" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B36">
+        <v>9</v>
+      </c>
+      <c r="C36">
+        <v>0</v>
+      </c>
+      <c r="D36" t="s">
+        <v>9</v>
+      </c>
+      <c r="E36">
+        <v>2.0750000000000002</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A37" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B37">
+        <v>9</v>
+      </c>
+      <c r="C37">
+        <v>0</v>
+      </c>
+      <c r="D37" t="s">
+        <v>10</v>
+      </c>
+      <c r="E37">
+        <v>2.0510000000000002</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A38" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B38">
+        <v>9</v>
+      </c>
+      <c r="C38">
+        <v>16</v>
+      </c>
+      <c r="D38" t="s">
+        <v>8</v>
+      </c>
+      <c r="E38">
+        <v>0.26100000000000001</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A39" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B39">
+        <v>9</v>
+      </c>
+      <c r="C39">
+        <v>16</v>
+      </c>
+      <c r="D39" t="s">
+        <v>9</v>
+      </c>
+      <c r="E39">
+        <v>0.20300000000000001</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A40" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B40">
+        <v>9</v>
+      </c>
+      <c r="C40">
+        <v>16</v>
+      </c>
+      <c r="D40" t="s">
+        <v>10</v>
+      </c>
+      <c r="E40">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A41" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B41">
+        <v>9</v>
+      </c>
+      <c r="C41">
+        <v>0</v>
+      </c>
+      <c r="D41" t="s">
+        <v>8</v>
+      </c>
+      <c r="E41">
+        <v>2.0259999999999998</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A42" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B42">
+        <v>9</v>
+      </c>
+      <c r="C42">
+        <v>0</v>
+      </c>
+      <c r="D42" t="s">
+        <v>9</v>
+      </c>
+      <c r="E42">
+        <v>2.056</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A43" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B43">
+        <v>9</v>
+      </c>
+      <c r="C43">
+        <v>0</v>
+      </c>
+      <c r="D43" t="s">
+        <v>10</v>
+      </c>
+      <c r="E43">
+        <v>2.081</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A44" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B44">
+        <v>9</v>
+      </c>
+      <c r="C44">
+        <v>16</v>
+      </c>
+      <c r="D44" t="s">
+        <v>8</v>
+      </c>
+      <c r="E44">
+        <v>0.104</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A45" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B45">
+        <v>9</v>
+      </c>
+      <c r="C45">
+        <v>16</v>
+      </c>
+      <c r="D45" t="s">
+        <v>9</v>
+      </c>
+      <c r="E45">
+        <v>0.17799999999999999</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A46" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B46">
+        <v>9</v>
+      </c>
+      <c r="C46">
+        <v>16</v>
+      </c>
+      <c r="D46" t="s">
+        <v>10</v>
+      </c>
+      <c r="E46">
+        <v>0.17299999999999999</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A47" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B47" t="s">
+        <v>11</v>
+      </c>
+      <c r="C47">
+        <v>0</v>
+      </c>
+      <c r="D47" t="s">
+        <v>11</v>
+      </c>
+      <c r="E47">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A48" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B48" t="s">
+        <v>11</v>
+      </c>
+      <c r="C48">
+        <v>16</v>
+      </c>
+      <c r="D48" t="s">
+        <v>11</v>
+      </c>
+      <c r="E48">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A49" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B49" t="s">
+        <v>11</v>
+      </c>
+      <c r="C49">
+        <v>0</v>
+      </c>
+      <c r="D49" t="s">
+        <v>11</v>
+      </c>
+      <c r="E49">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A50" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B50" t="s">
+        <v>11</v>
+      </c>
+      <c r="C50">
+        <v>16</v>
+      </c>
+      <c r="D50" t="s">
+        <v>11</v>
+      </c>
+      <c r="E50">
+        <v>0.05</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -19276,18 +20976,848 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DA40EA96-C7DC-4F46-BB79-8DC4E5D46CF8}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:E23"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A2" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B2">
+        <v>3</v>
+      </c>
+      <c r="C2">
+        <v>0</v>
+      </c>
+      <c r="D2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2">
+        <v>2.1930000000000001</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A3" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B3">
+        <v>3</v>
+      </c>
+      <c r="C3">
+        <v>0</v>
+      </c>
+      <c r="D3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E3">
+        <v>1.907</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A4" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4">
+        <v>3</v>
+      </c>
+      <c r="C4">
+        <v>0</v>
+      </c>
+      <c r="D4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E4">
+        <v>1.77</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A5" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B5">
+        <v>3</v>
+      </c>
+      <c r="C5">
+        <v>16</v>
+      </c>
+      <c r="D5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E5">
+        <v>1.1479999999999999</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A6" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B6">
+        <v>3</v>
+      </c>
+      <c r="C6">
+        <v>16</v>
+      </c>
+      <c r="D6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E6">
+        <v>0.50900000000000001</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A7" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B7">
+        <v>3</v>
+      </c>
+      <c r="C7">
+        <v>16</v>
+      </c>
+      <c r="D7" t="s">
+        <v>10</v>
+      </c>
+      <c r="E7">
+        <v>0.27</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A8" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B8">
+        <v>6</v>
+      </c>
+      <c r="C8">
+        <v>0</v>
+      </c>
+      <c r="D8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E8">
+        <v>1.9510000000000001</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A9" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B9">
+        <v>6</v>
+      </c>
+      <c r="C9">
+        <v>0</v>
+      </c>
+      <c r="D9" t="s">
+        <v>9</v>
+      </c>
+      <c r="E9">
+        <v>2.1219999999999999</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A10" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B10">
+        <v>6</v>
+      </c>
+      <c r="C10">
+        <v>0</v>
+      </c>
+      <c r="D10" t="s">
+        <v>10</v>
+      </c>
+      <c r="E10">
+        <v>2.1440000000000001</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A11" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B11">
+        <v>6</v>
+      </c>
+      <c r="C11">
+        <v>16</v>
+      </c>
+      <c r="D11" t="s">
+        <v>8</v>
+      </c>
+      <c r="E11">
+        <v>5.0999999999999997E-2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A12" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B12">
+        <v>6</v>
+      </c>
+      <c r="C12">
+        <v>16</v>
+      </c>
+      <c r="D12" t="s">
+        <v>9</v>
+      </c>
+      <c r="E12">
+        <v>7.1999999999999995E-2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A13" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B13">
+        <v>6</v>
+      </c>
+      <c r="C13">
+        <v>16</v>
+      </c>
+      <c r="D13" t="s">
+        <v>10</v>
+      </c>
+      <c r="E13">
+        <v>5.1999999999999998E-2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A14" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B14">
+        <v>9</v>
+      </c>
+      <c r="C14">
+        <v>0</v>
+      </c>
+      <c r="D14" t="s">
+        <v>8</v>
+      </c>
+      <c r="E14">
+        <v>2.056</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A15" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B15">
+        <v>9</v>
+      </c>
+      <c r="C15">
+        <v>0</v>
+      </c>
+      <c r="D15" t="s">
+        <v>9</v>
+      </c>
+      <c r="E15">
+        <v>2.0750000000000002</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A16" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B16">
+        <v>9</v>
+      </c>
+      <c r="C16">
+        <v>0</v>
+      </c>
+      <c r="D16" t="s">
+        <v>10</v>
+      </c>
+      <c r="E16">
+        <v>2.0510000000000002</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A17" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B17">
+        <v>9</v>
+      </c>
+      <c r="C17">
+        <v>16</v>
+      </c>
+      <c r="D17" t="s">
+        <v>8</v>
+      </c>
+      <c r="E17">
+        <v>0.26100000000000001</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A18" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B18">
+        <v>9</v>
+      </c>
+      <c r="C18">
+        <v>16</v>
+      </c>
+      <c r="D18" t="s">
+        <v>9</v>
+      </c>
+      <c r="E18">
+        <v>0.20300000000000001</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A19" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B19">
+        <v>9</v>
+      </c>
+      <c r="C19">
+        <v>16</v>
+      </c>
+      <c r="D19" t="s">
+        <v>10</v>
+      </c>
+      <c r="E19">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A20" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B20" t="s">
+        <v>13</v>
+      </c>
+      <c r="C20">
+        <v>0</v>
+      </c>
+      <c r="D20" t="s">
+        <v>11</v>
+      </c>
+      <c r="E20">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A21" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B21" t="s">
+        <v>13</v>
+      </c>
+      <c r="C21">
+        <v>16</v>
+      </c>
+      <c r="D21" t="s">
+        <v>11</v>
+      </c>
+      <c r="E21">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A22" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B22" t="s">
+        <v>12</v>
+      </c>
+      <c r="C22">
+        <v>0</v>
+      </c>
+      <c r="D22" t="s">
+        <v>11</v>
+      </c>
+      <c r="E22">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A23" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B23" t="s">
+        <v>12</v>
+      </c>
+      <c r="C23">
+        <v>16</v>
+      </c>
+      <c r="D23" t="s">
+        <v>11</v>
+      </c>
+      <c r="E23">
+        <v>0.05</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46236C33-E0E3-4D54-A61B-409978D4C792}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:G19"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A2" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B2">
+        <v>0</v>
+      </c>
+      <c r="C2">
+        <v>3</v>
+      </c>
+      <c r="D2">
+        <v>6</v>
+      </c>
+      <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G2">
+        <v>2.1930000000000001</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A3" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B3">
+        <v>0</v>
+      </c>
+      <c r="C3">
+        <v>3</v>
+      </c>
+      <c r="D3">
+        <v>6</v>
+      </c>
+      <c r="E3">
+        <v>0</v>
+      </c>
+      <c r="F3" t="s">
+        <v>9</v>
+      </c>
+      <c r="G3">
+        <v>1.907</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A4" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4">
+        <v>0</v>
+      </c>
+      <c r="C4">
+        <v>3</v>
+      </c>
+      <c r="D4">
+        <v>6</v>
+      </c>
+      <c r="E4">
+        <v>0</v>
+      </c>
+      <c r="F4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G4">
+        <v>1.77</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A5" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B5">
+        <v>0</v>
+      </c>
+      <c r="C5">
+        <v>3</v>
+      </c>
+      <c r="D5">
+        <v>6</v>
+      </c>
+      <c r="E5">
+        <v>16</v>
+      </c>
+      <c r="F5" t="s">
+        <v>8</v>
+      </c>
+      <c r="G5">
+        <v>1.1479999999999999</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A6" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B6">
+        <v>0</v>
+      </c>
+      <c r="C6">
+        <v>3</v>
+      </c>
+      <c r="D6">
+        <v>6</v>
+      </c>
+      <c r="E6">
+        <v>16</v>
+      </c>
+      <c r="F6" t="s">
+        <v>9</v>
+      </c>
+      <c r="G6">
+        <v>0.50900000000000001</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A7" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B7">
+        <v>0</v>
+      </c>
+      <c r="C7">
+        <v>3</v>
+      </c>
+      <c r="D7">
+        <v>6</v>
+      </c>
+      <c r="E7">
+        <v>16</v>
+      </c>
+      <c r="F7" t="s">
+        <v>10</v>
+      </c>
+      <c r="G7">
+        <v>0.27</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A8" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B8">
+        <v>0.5</v>
+      </c>
+      <c r="C8">
+        <v>6</v>
+      </c>
+      <c r="D8">
+        <v>6</v>
+      </c>
+      <c r="E8">
+        <v>0</v>
+      </c>
+      <c r="F8" t="s">
+        <v>8</v>
+      </c>
+      <c r="G8">
+        <v>1.9510000000000001</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A9" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B9">
+        <v>0.5</v>
+      </c>
+      <c r="C9">
+        <v>6</v>
+      </c>
+      <c r="D9">
+        <v>6</v>
+      </c>
+      <c r="E9">
+        <v>0</v>
+      </c>
+      <c r="F9" t="s">
+        <v>9</v>
+      </c>
+      <c r="G9">
+        <v>2.1219999999999999</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A10" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B10">
+        <v>0.5</v>
+      </c>
+      <c r="C10">
+        <v>6</v>
+      </c>
+      <c r="D10">
+        <v>6</v>
+      </c>
+      <c r="E10">
+        <v>0</v>
+      </c>
+      <c r="F10" t="s">
+        <v>10</v>
+      </c>
+      <c r="G10">
+        <v>2.1440000000000001</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A11" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B11">
+        <v>0.5</v>
+      </c>
+      <c r="C11">
+        <v>6</v>
+      </c>
+      <c r="D11">
+        <v>6</v>
+      </c>
+      <c r="E11">
+        <v>16</v>
+      </c>
+      <c r="F11" t="s">
+        <v>8</v>
+      </c>
+      <c r="G11">
+        <v>5.0999999999999997E-2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A12" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B12">
+        <v>0.5</v>
+      </c>
+      <c r="C12">
+        <v>6</v>
+      </c>
+      <c r="D12">
+        <v>6</v>
+      </c>
+      <c r="E12">
+        <v>16</v>
+      </c>
+      <c r="F12" t="s">
+        <v>9</v>
+      </c>
+      <c r="G12">
+        <v>7.1999999999999995E-2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A13" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B13">
+        <v>0.5</v>
+      </c>
+      <c r="C13">
+        <v>6</v>
+      </c>
+      <c r="D13">
+        <v>6</v>
+      </c>
+      <c r="E13">
+        <v>16</v>
+      </c>
+      <c r="F13" t="s">
+        <v>10</v>
+      </c>
+      <c r="G13">
+        <v>5.1999999999999998E-2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A14" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B14">
+        <v>1</v>
+      </c>
+      <c r="C14">
+        <v>9</v>
+      </c>
+      <c r="D14">
+        <v>6</v>
+      </c>
+      <c r="E14">
+        <v>0</v>
+      </c>
+      <c r="F14" t="s">
+        <v>8</v>
+      </c>
+      <c r="G14">
+        <v>2.056</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A15" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B15">
+        <v>1</v>
+      </c>
+      <c r="C15">
+        <v>9</v>
+      </c>
+      <c r="D15">
+        <v>6</v>
+      </c>
+      <c r="E15">
+        <v>0</v>
+      </c>
+      <c r="F15" t="s">
+        <v>9</v>
+      </c>
+      <c r="G15">
+        <v>2.0750000000000002</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A16" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B16">
+        <v>1</v>
+      </c>
+      <c r="C16">
+        <v>9</v>
+      </c>
+      <c r="D16">
+        <v>6</v>
+      </c>
+      <c r="E16">
+        <v>0</v>
+      </c>
+      <c r="F16" t="s">
+        <v>10</v>
+      </c>
+      <c r="G16">
+        <v>2.0510000000000002</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A17" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B17">
+        <v>1</v>
+      </c>
+      <c r="C17">
+        <v>9</v>
+      </c>
+      <c r="D17">
+        <v>6</v>
+      </c>
+      <c r="E17">
+        <v>16</v>
+      </c>
+      <c r="F17" t="s">
+        <v>8</v>
+      </c>
+      <c r="G17">
+        <v>0.26100000000000001</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A18" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B18">
+        <v>1</v>
+      </c>
+      <c r="C18">
+        <v>9</v>
+      </c>
+      <c r="D18">
+        <v>6</v>
+      </c>
+      <c r="E18">
+        <v>16</v>
+      </c>
+      <c r="F18" t="s">
+        <v>9</v>
+      </c>
+      <c r="G18">
+        <v>0.20300000000000001</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A19" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B19">
+        <v>1</v>
+      </c>
+      <c r="C19">
+        <v>9</v>
+      </c>
+      <c r="D19">
+        <v>6</v>
+      </c>
+      <c r="E19">
+        <v>16</v>
+      </c>
+      <c r="F19" t="s">
+        <v>10</v>
+      </c>
+      <c r="G19">
+        <v>0.3</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>